--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46269.320240694564</v>
+        <v>46270.320242731366</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46270.320242731366</v>
+        <v>46277.320240902714</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46277.320240902714</v>
+        <v>46282.320259398315</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46282.320259398315</v>
+        <v>46286.32025442133</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46286.32025442133</v>
+        <v>46287.320252592675</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46287.320252592675</v>
+        <v>46289.32029167842</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46289.32029167842</v>
+        <v>46291.320251990575</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46291.320251990575</v>
+        <v>46293.32024035882</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46293.32024035882</v>
+        <v>46294.32026015036</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46294.32026015036</v>
+        <v>46296.32024885435</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46296.32024885435</v>
+        <v>46297.320242511574</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46297.320242511574</v>
+        <v>46303.3202500809</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46303.3202500809</v>
+        <v>46307.32023641188</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46307.32023641188</v>
+        <v>46309.32024784712</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46309.32024784712</v>
+        <v>46311.3202493405</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46311.3202493405</v>
+        <v>46313.32025608793</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46313.32025608793</v>
+        <v>46314.32024456002</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46314.32024456002</v>
+        <v>46318.32025664346</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46318.32025664346</v>
+        <v>46319.32024827553</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46319.32024827553</v>
+        <v>46321.32023027772</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46321.32023027772</v>
+        <v>46322.32025613403</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
+++ b/data_xlsx/zone_struktura_budynkow_zrodla_co_polska.xlsx
@@ -905,7 +905,7 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="8">
-        <v>46322.32025613403</v>
+        <v>46325.320255694445</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
     </row>
